--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/114.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/114.xlsx
@@ -426,13 +426,13 @@
         <v>-16.26794877488715</v>
       </c>
       <c r="E2">
-        <v>-14.26120374740931</v>
+        <v>-14.90580485155714</v>
       </c>
       <c r="F2">
-        <v>0.5730022944539803</v>
+        <v>0.2036837999572515</v>
       </c>
       <c r="G2">
-        <v>-13.58345586048716</v>
+        <v>-13.79508910517615</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.21618927542748</v>
       </c>
       <c r="E3">
-        <v>-15.21605513429665</v>
+        <v>-15.84422240627064</v>
       </c>
       <c r="F3">
-        <v>0.6559028190239464</v>
+        <v>-0.1659494741525411</v>
       </c>
       <c r="G3">
-        <v>-13.89998374058796</v>
+        <v>-12.91476704337362</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.20371362560664</v>
       </c>
       <c r="E4">
-        <v>-13.99183199953705</v>
+        <v>-15.99025663607</v>
       </c>
       <c r="F4">
-        <v>0.6749362168380706</v>
+        <v>-0.1016018943030755</v>
       </c>
       <c r="G4">
-        <v>-12.89958819207606</v>
+        <v>-13.00899841160344</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.2173792814008</v>
       </c>
       <c r="E5">
-        <v>-16.35851667084776</v>
+        <v>-15.70815987623618</v>
       </c>
       <c r="F5">
-        <v>0.3980759500048087</v>
+        <v>0.7550376879539772</v>
       </c>
       <c r="G5">
-        <v>-12.72266932791187</v>
+        <v>-12.75467568218555</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.2329316548216</v>
       </c>
       <c r="E6">
-        <v>-16.68651857169733</v>
+        <v>-16.31654677374467</v>
       </c>
       <c r="F6">
-        <v>0.5352834131349076</v>
+        <v>0.8195708221016699</v>
       </c>
       <c r="G6">
-        <v>-11.90231945382601</v>
+        <v>-12.7120921349139</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.22995628180885</v>
       </c>
       <c r="E7">
-        <v>-16.20944836346326</v>
+        <v>-16.08309488170125</v>
       </c>
       <c r="F7">
-        <v>0.2087227588684809</v>
+        <v>0.7467308196387038</v>
       </c>
       <c r="G7">
-        <v>-11.03315227521806</v>
+        <v>-13.41300745757948</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.17996792841426</v>
       </c>
       <c r="E8">
-        <v>-17.8766649395492</v>
+        <v>-17.07030221537338</v>
       </c>
       <c r="F8">
-        <v>0.9730540479619735</v>
+        <v>1.014117876853551</v>
       </c>
       <c r="G8">
-        <v>-11.86992907626978</v>
+        <v>-12.85196268394811</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.05724439834052</v>
       </c>
       <c r="E9">
-        <v>-18.2870986527604</v>
+        <v>-18.12472568874137</v>
       </c>
       <c r="F9">
-        <v>0.9873997146436554</v>
+        <v>0.5697111907626579</v>
       </c>
       <c r="G9">
-        <v>-11.32016995238179</v>
+        <v>-12.82023110495419</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.84948278762149</v>
       </c>
       <c r="E10">
-        <v>-18.5120958838315</v>
+        <v>-18.75228614519834</v>
       </c>
       <c r="F10">
-        <v>1.079066851437449</v>
+        <v>0.4736818712257224</v>
       </c>
       <c r="G10">
-        <v>-10.98180240335842</v>
+        <v>-12.72744644512504</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.53883442941543</v>
       </c>
       <c r="E11">
-        <v>-18.60139286278875</v>
+        <v>-18.56661871088385</v>
       </c>
       <c r="F11">
-        <v>0.945477697122778</v>
+        <v>1.424380086968451</v>
       </c>
       <c r="G11">
-        <v>-11.19709711141385</v>
+        <v>-11.98013713727212</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.12071948593481</v>
       </c>
       <c r="E12">
-        <v>-19.78187546710826</v>
+        <v>-19.05827513389662</v>
       </c>
       <c r="F12">
-        <v>1.59215099379224</v>
+        <v>1.095062625985507</v>
       </c>
       <c r="G12">
-        <v>-10.40595618062097</v>
+        <v>-11.05644527363237</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.58960116621979</v>
       </c>
       <c r="E13">
-        <v>-19.74525369780823</v>
+        <v>-19.51659745973893</v>
       </c>
       <c r="F13">
-        <v>1.193270551791805</v>
+        <v>1.749267439081222</v>
       </c>
       <c r="G13">
-        <v>-10.31767055217969</v>
+        <v>-11.32825430458869</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.9674126372163</v>
       </c>
       <c r="E14">
-        <v>-20.93596612491107</v>
+        <v>-20.27146690597354</v>
       </c>
       <c r="F14">
-        <v>1.170598135977183</v>
+        <v>1.918688453771388</v>
       </c>
       <c r="G14">
-        <v>-9.930131470261527</v>
+        <v>-11.70083303121489</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.26798828835677</v>
       </c>
       <c r="E15">
-        <v>-20.35748979822324</v>
+        <v>-19.91471372364926</v>
       </c>
       <c r="F15">
-        <v>1.268550924623419</v>
+        <v>1.784181468374416</v>
       </c>
       <c r="G15">
-        <v>-9.361585000438172</v>
+        <v>-10.41260375606383</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.51658384385735</v>
       </c>
       <c r="E16">
-        <v>-22.60678736630712</v>
+        <v>-22.65735230707676</v>
       </c>
       <c r="F16">
-        <v>1.648352408602575</v>
+        <v>2.403051441536315</v>
       </c>
       <c r="G16">
-        <v>-10.50296509655824</v>
+        <v>-10.2027880008759</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.74801677017889</v>
       </c>
       <c r="E17">
-        <v>-22.86344315916584</v>
+        <v>-22.53813117187682</v>
       </c>
       <c r="F17">
-        <v>1.132902448945388</v>
+        <v>2.351787096446665</v>
       </c>
       <c r="G17">
-        <v>-8.62177738877724</v>
+        <v>-10.37821711954742</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.99905311001987</v>
       </c>
       <c r="E18">
-        <v>-23.68516646717568</v>
+        <v>-23.87851872188118</v>
       </c>
       <c r="F18">
-        <v>1.959540220607849</v>
+        <v>2.607156199381697</v>
       </c>
       <c r="G18">
-        <v>-6.984557023967292</v>
+        <v>-10.03376478782287</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.30321424186618</v>
       </c>
       <c r="E19">
-        <v>-23.86109315389967</v>
+        <v>-23.2025941630223</v>
       </c>
       <c r="F19">
-        <v>2.584467216219018</v>
+        <v>2.48311977795611</v>
       </c>
       <c r="G19">
-        <v>-7.849384077373261</v>
+        <v>-8.683879912548427</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.686927361199453</v>
       </c>
       <c r="E20">
-        <v>-24.54990574978438</v>
+        <v>-24.38361112727471</v>
       </c>
       <c r="F20">
-        <v>2.117831290874001</v>
+        <v>3.311889767313376</v>
       </c>
       <c r="G20">
-        <v>-7.547783447109038</v>
+        <v>-8.738864763410183</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.185277318054396</v>
       </c>
       <c r="E21">
-        <v>-25.34775494282578</v>
+        <v>-25.76257674735041</v>
       </c>
       <c r="F21">
-        <v>2.736517366472479</v>
+        <v>2.744552530279634</v>
       </c>
       <c r="G21">
-        <v>-6.931343314969046</v>
+        <v>-8.64494458646106</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.80951084217784</v>
       </c>
       <c r="E22">
-        <v>-24.92695555261103</v>
+        <v>-25.86612030553579</v>
       </c>
       <c r="F22">
-        <v>2.587076573537836</v>
+        <v>2.7815888368588</v>
       </c>
       <c r="G22">
-        <v>-6.274660191253675</v>
+        <v>-7.969755513181162</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.568940887388562</v>
       </c>
       <c r="E23">
-        <v>-26.4246305903238</v>
+        <v>-26.26926770406865</v>
       </c>
       <c r="F23">
-        <v>2.581155403342626</v>
+        <v>3.071020407396947</v>
       </c>
       <c r="G23">
-        <v>-6.925947125740034</v>
+        <v>-7.290067408513394</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.461149683002485</v>
       </c>
       <c r="E24">
-        <v>-27.85715900096223</v>
+        <v>-26.40529853478506</v>
       </c>
       <c r="F24">
-        <v>3.548647111442308</v>
+        <v>3.570330456577988</v>
       </c>
       <c r="G24">
-        <v>-6.667022738022556</v>
+        <v>-7.947929086440746</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.482727346075967</v>
       </c>
       <c r="E25">
-        <v>-29.14605327302537</v>
+        <v>-27.44403990266449</v>
       </c>
       <c r="F25">
-        <v>2.888676861223109</v>
+        <v>3.545938350035154</v>
       </c>
       <c r="G25">
-        <v>-5.330929595464716</v>
+        <v>-7.115376541497132</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.613586313670343</v>
       </c>
       <c r="E26">
-        <v>-28.95116133715726</v>
+        <v>-27.76113723810359</v>
       </c>
       <c r="F26">
-        <v>3.184457039536311</v>
+        <v>3.944974525107315</v>
       </c>
       <c r="G26">
-        <v>-4.901644534296342</v>
+        <v>-7.093132986018769</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.83138760742929</v>
       </c>
       <c r="E27">
-        <v>-27.57571434138551</v>
+        <v>-28.80024994085164</v>
       </c>
       <c r="F27">
-        <v>2.949338206130117</v>
+        <v>3.531150335160377</v>
       </c>
       <c r="G27">
-        <v>-6.591568784091487</v>
+        <v>-7.09008728412264</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.117111322847981</v>
       </c>
       <c r="E28">
-        <v>-29.66250535546714</v>
+        <v>-28.90756118941141</v>
       </c>
       <c r="F28">
-        <v>3.434923864181576</v>
+        <v>2.883282532696078</v>
       </c>
       <c r="G28">
-        <v>-6.338659657618865</v>
+        <v>-6.949283161246357</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.438735163610113</v>
       </c>
       <c r="E29">
-        <v>-26.8683621729134</v>
+        <v>-29.47056145617802</v>
       </c>
       <c r="F29">
-        <v>2.600267496060016</v>
+        <v>3.551125586711485</v>
       </c>
       <c r="G29">
-        <v>-4.688379190656493</v>
+        <v>-6.954288706101735</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.774550145262596</v>
       </c>
       <c r="E30">
-        <v>-28.29180193621843</v>
+        <v>-27.86870660968179</v>
       </c>
       <c r="F30">
-        <v>2.574024816739328</v>
+        <v>3.046419552268608</v>
       </c>
       <c r="G30">
-        <v>-5.551206674556743</v>
+        <v>-7.365637231538337</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.10072957570051</v>
       </c>
       <c r="E31">
-        <v>-28.55154614835039</v>
+        <v>-28.93525280796831</v>
       </c>
       <c r="F31">
-        <v>3.342976739205636</v>
+        <v>3.25908797232413</v>
       </c>
       <c r="G31">
-        <v>-7.595630761788124</v>
+        <v>-7.956165723742453</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.40722988187538</v>
       </c>
       <c r="E32">
-        <v>-27.90900097140204</v>
+        <v>-28.60957401428467</v>
       </c>
       <c r="F32">
-        <v>2.55866854182623</v>
+        <v>3.14584186468741</v>
       </c>
       <c r="G32">
-        <v>-5.666602360419118</v>
+        <v>-7.011379063926467</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.67741858053867</v>
       </c>
       <c r="E33">
-        <v>-26.56466459206299</v>
+        <v>-27.9937015492415</v>
       </c>
       <c r="F33">
-        <v>2.447973805790133</v>
+        <v>3.223829342191372</v>
       </c>
       <c r="G33">
-        <v>-4.892619987156289</v>
+        <v>-7.54241705278988</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.90980547677935</v>
       </c>
       <c r="E34">
-        <v>-27.25763432708675</v>
+        <v>-27.97091879650891</v>
       </c>
       <c r="F34">
-        <v>2.486497860224726</v>
+        <v>2.820195728033673</v>
       </c>
       <c r="G34">
-        <v>-5.901051884964764</v>
+        <v>-6.412796014425304</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.10822943444975</v>
       </c>
       <c r="E35">
-        <v>-27.44188434903683</v>
+        <v>-27.48738645586591</v>
       </c>
       <c r="F35">
-        <v>2.750803390701159</v>
+        <v>3.345272973646196</v>
       </c>
       <c r="G35">
-        <v>-6.187639191208392</v>
+        <v>-7.017050028435238</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.2762408601041</v>
       </c>
       <c r="E36">
-        <v>-27.43555807084812</v>
+        <v>-28.16639943399802</v>
       </c>
       <c r="F36">
-        <v>3.070143994684785</v>
+        <v>3.066719523841612</v>
       </c>
       <c r="G36">
-        <v>-6.747932471002344</v>
+        <v>-7.696420320731236</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.42365979571399</v>
       </c>
       <c r="E37">
-        <v>-27.12368206593986</v>
+        <v>-28.90678229188208</v>
       </c>
       <c r="F37">
-        <v>2.388927777318584</v>
+        <v>3.817902965517871</v>
       </c>
       <c r="G37">
-        <v>-5.551858852027978</v>
+        <v>-7.154407873405139</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.56163474807295</v>
       </c>
       <c r="E38">
-        <v>-27.36542559389133</v>
+        <v>-26.82734778382593</v>
       </c>
       <c r="F38">
-        <v>2.938741730313505</v>
+        <v>3.575226107928533</v>
       </c>
       <c r="G38">
-        <v>-5.064847808291334</v>
+        <v>-6.385331728631511</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.70686741494858</v>
       </c>
       <c r="E39">
-        <v>-26.88802933552871</v>
+        <v>-26.52061612539038</v>
       </c>
       <c r="F39">
-        <v>2.907343292277793</v>
+        <v>3.52019103442134</v>
       </c>
       <c r="G39">
-        <v>-6.705322439366385</v>
+        <v>-6.827981462141921</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.85987865198426</v>
       </c>
       <c r="E40">
-        <v>-26.30530982869569</v>
+        <v>-27.04009096423227</v>
       </c>
       <c r="F40">
-        <v>2.775202124183215</v>
+        <v>3.070143994684785</v>
       </c>
       <c r="G40">
-        <v>-5.820373890172725</v>
+        <v>-7.488746488507215</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.03192771795016</v>
       </c>
       <c r="E41">
-        <v>-24.88521660768233</v>
+        <v>-27.10205860255324</v>
       </c>
       <c r="F41">
-        <v>2.61785704949106</v>
+        <v>3.328140679021497</v>
       </c>
       <c r="G41">
-        <v>-6.145128475938611</v>
+        <v>-7.322520686434869</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.22506828835231</v>
       </c>
       <c r="E42">
-        <v>-26.74482993045816</v>
+        <v>-26.16500864699005</v>
       </c>
       <c r="F42">
-        <v>3.007603912508228</v>
+        <v>3.171739943168533</v>
       </c>
       <c r="G42">
-        <v>-5.914644984949011</v>
+        <v>-8.091166460288393</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.44081828103895</v>
       </c>
       <c r="E43">
-        <v>-22.42274565416139</v>
+        <v>-25.31764059067477</v>
       </c>
       <c r="F43">
-        <v>2.819330912465151</v>
+        <v>3.072267928705563</v>
       </c>
       <c r="G43">
-        <v>-6.106434819675609</v>
+        <v>-8.434364095253558</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.67020859879535</v>
       </c>
       <c r="E44">
-        <v>-25.21254829437877</v>
+        <v>-26.09610338648934</v>
       </c>
       <c r="F44">
-        <v>2.810866654343346</v>
+        <v>3.200058511200637</v>
       </c>
       <c r="G44">
-        <v>-6.147535242545661</v>
+        <v>-8.253674519720137</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.90695479277269</v>
       </c>
       <c r="E45">
-        <v>-24.20404807592256</v>
+        <v>-24.45177824651217</v>
       </c>
       <c r="F45">
-        <v>3.042948692850878</v>
+        <v>3.270811027808548</v>
       </c>
       <c r="G45">
-        <v>-5.418099570059265</v>
+        <v>-7.737073819953486</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.14666263301922</v>
       </c>
       <c r="E46">
-        <v>-22.34733297651165</v>
+        <v>-23.56138968712403</v>
       </c>
       <c r="F46">
-        <v>2.318393949705011</v>
+        <v>3.658354433534269</v>
       </c>
       <c r="G46">
-        <v>-5.750064524009684</v>
+        <v>-6.696003253673337</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.37297557911171</v>
       </c>
       <c r="E47">
-        <v>-21.56735314190452</v>
+        <v>-25.45067810007211</v>
       </c>
       <c r="F47">
-        <v>3.437350980671778</v>
+        <v>3.197068104876531</v>
       </c>
       <c r="G47">
-        <v>-7.175138509572055</v>
+        <v>-8.181680085877606</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.57919792413928</v>
       </c>
       <c r="E48">
-        <v>-21.9535142344346</v>
+        <v>-24.00511221276561</v>
       </c>
       <c r="F48">
-        <v>3.202652957906205</v>
+        <v>3.255143286751999</v>
       </c>
       <c r="G48">
-        <v>-6.77306944328203</v>
+        <v>-8.271452149266024</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.75323988588988</v>
       </c>
       <c r="E49">
-        <v>-22.46822964709443</v>
+        <v>-22.74547641126603</v>
       </c>
       <c r="F49">
-        <v>2.209172050911091</v>
+        <v>3.105023232547061</v>
       </c>
       <c r="G49">
-        <v>-6.488743239641725</v>
+        <v>-7.637797180321821</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.89437165514136</v>
       </c>
       <c r="E50">
-        <v>-19.94691570231781</v>
+        <v>-22.37462608935588</v>
       </c>
       <c r="F50">
-        <v>3.542230577540223</v>
+        <v>2.964735899413354</v>
       </c>
       <c r="G50">
-        <v>-6.793190939069721</v>
+        <v>-7.706835296997783</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.98983589247865</v>
       </c>
       <c r="E51">
-        <v>-23.17023821623749</v>
+        <v>-21.88270701485066</v>
       </c>
       <c r="F51">
-        <v>3.064441513483913</v>
+        <v>3.028193812672213</v>
       </c>
       <c r="G51">
-        <v>-8.609021856814428</v>
+        <v>-9.112870335163805</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.03819388135082</v>
       </c>
       <c r="E52">
-        <v>-19.23316932854686</v>
+        <v>-21.76053331459773</v>
       </c>
       <c r="F52">
-        <v>2.592351617158864</v>
+        <v>2.826350497836474</v>
       </c>
       <c r="G52">
-        <v>-7.796220026558105</v>
+        <v>-8.50031678348692</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-14.03913611788242</v>
       </c>
       <c r="E53">
-        <v>-19.85486541116389</v>
+        <v>-20.33369719578694</v>
       </c>
       <c r="F53">
-        <v>3.170038476523183</v>
+        <v>3.152251771650272</v>
       </c>
       <c r="G53">
-        <v>-7.855045110245415</v>
+        <v>-9.058921685055843</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.9928734062408</v>
       </c>
       <c r="E54">
-        <v>-19.38786200064888</v>
+        <v>-21.14717868110282</v>
       </c>
       <c r="F54">
-        <v>2.988811569608318</v>
+        <v>3.010204986153019</v>
       </c>
       <c r="G54">
-        <v>-7.519312755471306</v>
+        <v>-8.25288660988179</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.8998500304935</v>
       </c>
       <c r="E55">
-        <v>-19.31969488141142</v>
+        <v>-20.55312440382861</v>
       </c>
       <c r="F55">
-        <v>3.023879675238433</v>
+        <v>2.932789082156988</v>
       </c>
       <c r="G55">
-        <v>-7.690428233305155</v>
+        <v>-8.749067864762216</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.76099224794195</v>
       </c>
       <c r="E56">
-        <v>-18.60624738692498</v>
+        <v>-20.08566361743882</v>
       </c>
       <c r="F56">
-        <v>2.874029668806808</v>
+        <v>2.902610000938196</v>
       </c>
       <c r="G56">
-        <v>-8.07174017906395</v>
+        <v>-9.140387589686227</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.58765305531438</v>
       </c>
       <c r="E57">
-        <v>-19.51321921812921</v>
+        <v>-18.30779830744946</v>
       </c>
       <c r="F57">
-        <v>2.557460782152949</v>
+        <v>3.317519352182801</v>
       </c>
       <c r="G57">
-        <v>-8.568298836135853</v>
+        <v>-9.087041458866413</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.3784709587482</v>
       </c>
       <c r="E58">
-        <v>-18.5922679876633</v>
+        <v>-18.98343304397186</v>
       </c>
       <c r="F58">
-        <v>2.30331766297406</v>
+        <v>2.827974097945961</v>
       </c>
       <c r="G58">
-        <v>-7.389367221963833</v>
+        <v>-7.898866801548747</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.14190695268308</v>
       </c>
       <c r="E59">
-        <v>-17.44893245562871</v>
+        <v>-18.35655638709005</v>
       </c>
       <c r="F59">
-        <v>2.286463699796702</v>
+        <v>2.735342741495309</v>
       </c>
       <c r="G59">
-        <v>-7.42871967678915</v>
+        <v>-9.040561399495045</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.87996736649369</v>
       </c>
       <c r="E60">
-        <v>-16.53836954453639</v>
+        <v>-18.57654965438267</v>
       </c>
       <c r="F60">
-        <v>2.298418698153904</v>
+        <v>2.856594191712684</v>
       </c>
       <c r="G60">
-        <v>-8.09604289386774</v>
+        <v>-8.324917459725253</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.60478864804427</v>
       </c>
       <c r="E61">
-        <v>-18.06286673379659</v>
+        <v>-19.05312173047589</v>
       </c>
       <c r="F61">
-        <v>2.431224216905526</v>
+        <v>3.567094853502653</v>
       </c>
       <c r="G61">
-        <v>-6.957973343286944</v>
+        <v>-9.55732100544758</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.31657826376958</v>
       </c>
       <c r="E62">
-        <v>-17.68081749566548</v>
+        <v>-17.4084841257922</v>
       </c>
       <c r="F62">
-        <v>2.961717328597552</v>
+        <v>3.014080088863315</v>
       </c>
       <c r="G62">
-        <v>-8.468045585570103</v>
+        <v>-8.437240959327184</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.01748265410207</v>
       </c>
       <c r="E63">
-        <v>-17.3464938451012</v>
+        <v>-17.15911011913781</v>
       </c>
       <c r="F63">
-        <v>2.736638308113287</v>
+        <v>2.7527980994071</v>
       </c>
       <c r="G63">
-        <v>-7.211951775968751</v>
+        <v>-9.346959010245671</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.71475438207044</v>
       </c>
       <c r="E64">
-        <v>-15.86039811542604</v>
+        <v>-17.2392233528075</v>
       </c>
       <c r="F64">
-        <v>2.359777528414069</v>
+        <v>2.925032249797173</v>
       </c>
       <c r="G64">
-        <v>-7.858772784522634</v>
+        <v>-9.22732251554749</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.40900002133194</v>
       </c>
       <c r="E65">
-        <v>-15.71101281486101</v>
+        <v>-18.34614995382042</v>
       </c>
       <c r="F65">
-        <v>2.925994812719226</v>
+        <v>2.380246486937245</v>
       </c>
       <c r="G65">
-        <v>-7.952868420385339</v>
+        <v>-9.089901770212343</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.1019877004686</v>
       </c>
       <c r="E66">
-        <v>-17.46825998269345</v>
+        <v>-17.84521921603994</v>
       </c>
       <c r="F66">
-        <v>2.513408203672071</v>
+        <v>2.799314242543903</v>
       </c>
       <c r="G66">
-        <v>-9.188079308724969</v>
+        <v>-8.712658484921311</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.78925233047557</v>
       </c>
       <c r="E67">
-        <v>-14.6615978337455</v>
+        <v>-16.30179753390168</v>
       </c>
       <c r="F67">
-        <v>2.382347226670745</v>
+        <v>2.642611980956321</v>
       </c>
       <c r="G67">
-        <v>-7.77161936265578</v>
+        <v>-9.431987061876313</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.48009336370403</v>
       </c>
       <c r="E68">
-        <v>-16.16189485790872</v>
+        <v>-17.78499504021194</v>
       </c>
       <c r="F68">
-        <v>2.528209472425293</v>
+        <v>2.438313385138684</v>
       </c>
       <c r="G68">
-        <v>-9.324473784942942</v>
+        <v>-8.771533226791711</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.17046109313466</v>
       </c>
       <c r="E69">
-        <v>-15.19497961626495</v>
+        <v>-16.9919686719887</v>
       </c>
       <c r="F69">
-        <v>2.282220801959562</v>
+        <v>2.518368467680034</v>
       </c>
       <c r="G69">
-        <v>-9.394985094383879</v>
+        <v>-8.158433435100845</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.862281211547348</v>
       </c>
       <c r="E70">
-        <v>-15.66434236173796</v>
+        <v>-16.72271919291465</v>
       </c>
       <c r="F70">
-        <v>2.518988086497329</v>
+        <v>2.497740462615521</v>
       </c>
       <c r="G70">
-        <v>-7.882155167666506</v>
+        <v>-9.786616010588581</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.558571356812768</v>
       </c>
       <c r="E71">
-        <v>-16.68977001603484</v>
+        <v>-15.93252764942021</v>
       </c>
       <c r="F71">
-        <v>2.722625645127531</v>
+        <v>2.162529995929062</v>
       </c>
       <c r="G71">
-        <v>-7.358999587732098</v>
+        <v>-9.253396372214789</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.26582028906517</v>
       </c>
       <c r="E72">
-        <v>-17.47158841108908</v>
+        <v>-15.97658970151485</v>
       </c>
       <c r="F72">
-        <v>2.583022543468536</v>
+        <v>2.523499375372975</v>
       </c>
       <c r="G72">
-        <v>-7.575446365635188</v>
+        <v>-8.866608784134041</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.985683179960715</v>
       </c>
       <c r="E73">
-        <v>-14.83753810589151</v>
+        <v>-17.5710789850376</v>
       </c>
       <c r="F73">
-        <v>2.41010416160375</v>
+        <v>2.076641550137198</v>
       </c>
       <c r="G73">
-        <v>-7.381776141042284</v>
+        <v>-8.433099466857557</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.719466059347964</v>
       </c>
       <c r="E74">
-        <v>-16.53436184503961</v>
+        <v>-16.9469828111965</v>
       </c>
       <c r="F74">
-        <v>2.390244881489035</v>
+        <v>1.867127553151536</v>
       </c>
       <c r="G74">
-        <v>-6.571407561757326</v>
+        <v>-8.33101548460859</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.477964436003019</v>
       </c>
       <c r="E75">
-        <v>-15.79791875954221</v>
+        <v>-18.90119595599256</v>
       </c>
       <c r="F75">
-        <v>2.326876431909678</v>
+        <v>2.31950893222918</v>
       </c>
       <c r="G75">
-        <v>-6.917359570611165</v>
+        <v>-8.490792343970435</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.261226008832832</v>
       </c>
       <c r="E76">
-        <v>-14.62576401892281</v>
+        <v>-16.84114331668923</v>
       </c>
       <c r="F76">
-        <v>2.083697583674244</v>
+        <v>2.476035579927368</v>
       </c>
       <c r="G76">
-        <v>-6.978151118348802</v>
+        <v>-8.944568821038338</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.075127431343544</v>
       </c>
       <c r="E77">
-        <v>-16.68714350111039</v>
+        <v>-17.94110512467836</v>
       </c>
       <c r="F77">
-        <v>2.139822788683522</v>
+        <v>2.107635744880344</v>
       </c>
       <c r="G77">
-        <v>-8.205244549026139</v>
+        <v>-7.854035393855937</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.919235453959939</v>
       </c>
       <c r="E78">
-        <v>-18.19749373757063</v>
+        <v>-18.82082007083042</v>
       </c>
       <c r="F78">
-        <v>1.472099019574119</v>
+        <v>1.881406950440994</v>
       </c>
       <c r="G78">
-        <v>-5.929456365691711</v>
+        <v>-7.836919873417905</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.80075444663358</v>
       </c>
       <c r="E79">
-        <v>-16.01632706093215</v>
+        <v>-18.86862264245539</v>
       </c>
       <c r="F79">
-        <v>1.879148820900962</v>
+        <v>1.542062930414565</v>
       </c>
       <c r="G79">
-        <v>-6.883280814829908</v>
+        <v>-7.104855627773328</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.715370583826954</v>
       </c>
       <c r="E80">
-        <v>-17.58285754593155</v>
+        <v>-19.41350222048031</v>
       </c>
       <c r="F80">
-        <v>1.387481289378149</v>
+        <v>2.153873556569807</v>
       </c>
       <c r="G80">
-        <v>-7.534375737674989</v>
+        <v>-8.358029536209044</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.661139236288947</v>
       </c>
       <c r="E81">
-        <v>-18.40878780629452</v>
+        <v>-19.50846884889516</v>
       </c>
       <c r="F81">
-        <v>1.729209350789835</v>
+        <v>1.875779022306374</v>
       </c>
       <c r="G81">
-        <v>-6.722520723442899</v>
+        <v>-7.026551294132947</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.638887152532758</v>
       </c>
       <c r="E82">
-        <v>-18.96972988162464</v>
+        <v>-19.54418039491965</v>
       </c>
       <c r="F82">
-        <v>1.969374598413884</v>
+        <v>1.832107492830784</v>
       </c>
       <c r="G82">
-        <v>-6.526089503870243</v>
+        <v>-6.221227986249838</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.643723198305638</v>
       </c>
       <c r="E83">
-        <v>-21.28893350296493</v>
+        <v>-21.9257094040275</v>
       </c>
       <c r="F83">
-        <v>2.026666144726304</v>
+        <v>1.895012056664573</v>
       </c>
       <c r="G83">
-        <v>-6.825922302816495</v>
+        <v>-6.114502619154814</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.673768104469381</v>
       </c>
       <c r="E84">
-        <v>-20.54571129187805</v>
+        <v>-21.7927534071623</v>
       </c>
       <c r="F84">
-        <v>1.214243157695883</v>
+        <v>1.586799740370155</v>
       </c>
       <c r="G84">
-        <v>-5.510414132421842</v>
+        <v>-7.276715978353513</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.725271877008937</v>
       </c>
       <c r="E85">
-        <v>-21.17683565737905</v>
+        <v>-23.51076587619228</v>
       </c>
       <c r="F85">
-        <v>1.497563033536176</v>
+        <v>1.453025031757258</v>
       </c>
       <c r="G85">
-        <v>-5.721170082542925</v>
+        <v>-7.035976417283251</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.80273380165138</v>
       </c>
       <c r="E86">
-        <v>-22.3830807503282</v>
+        <v>-25.13944060999894</v>
       </c>
       <c r="F86">
-        <v>1.418692516380829</v>
+        <v>1.246677054985095</v>
       </c>
       <c r="G86">
-        <v>-5.605817433772559</v>
+        <v>-6.839853078445748</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.900157965357858</v>
       </c>
       <c r="E87">
-        <v>-25.302424918009</v>
+        <v>-24.11999054139219</v>
       </c>
       <c r="F87">
-        <v>0.9867718121523333</v>
+        <v>1.213149712724188</v>
       </c>
       <c r="G87">
-        <v>-6.215388183918563</v>
+        <v>-6.885488948704602</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.021043995121957</v>
       </c>
       <c r="E88">
-        <v>-25.107596380777</v>
+        <v>-26.73003993434911</v>
       </c>
       <c r="F88">
-        <v>0.7595473200948177</v>
+        <v>1.357819109418705</v>
       </c>
       <c r="G88">
-        <v>-6.200871441728859</v>
+        <v>-6.439323415831484</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.167948431602809</v>
       </c>
       <c r="E89">
-        <v>-27.33342286807912</v>
+        <v>-27.23769092755697</v>
       </c>
       <c r="F89">
-        <v>1.146174551473042</v>
+        <v>0.981067674216656</v>
       </c>
       <c r="G89">
-        <v>-6.31520113192759</v>
+        <v>-7.388023140474889</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.343213504358385</v>
       </c>
       <c r="E90">
-        <v>-28.55535912346484</v>
+        <v>-29.83189745419805</v>
       </c>
       <c r="F90">
-        <v>1.298322449080033</v>
+        <v>0.7955547943597067</v>
       </c>
       <c r="G90">
-        <v>-7.167779166838256</v>
+        <v>-5.82462132009961</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.547703183130556</v>
       </c>
       <c r="E91">
-        <v>-28.19695757660178</v>
+        <v>-29.69571039112838</v>
       </c>
       <c r="F91">
-        <v>0.9347370853780795</v>
+        <v>1.118159165910363</v>
       </c>
       <c r="G91">
-        <v>-6.259762736326954</v>
+        <v>-6.795627500586624</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.785471639912489</v>
       </c>
       <c r="E92">
-        <v>-32.01261807614677</v>
+        <v>-30.95821724514882</v>
       </c>
       <c r="F92">
-        <v>0.3548964707664816</v>
+        <v>0.8577419920226711</v>
       </c>
       <c r="G92">
-        <v>-6.16193942618703</v>
+        <v>-7.027438520337471</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.063664391254651</v>
       </c>
       <c r="E93">
-        <v>-33.08809442517642</v>
+        <v>-32.57361449316499</v>
       </c>
       <c r="F93">
-        <v>0.5042610539000661</v>
+        <v>0.4262984274181878</v>
       </c>
       <c r="G93">
-        <v>-6.070349873297554</v>
+        <v>-8.113545748133866</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.374747082176158</v>
       </c>
       <c r="E94">
-        <v>-33.97784446972948</v>
+        <v>-35.15853311961634</v>
       </c>
       <c r="F94">
-        <v>0.3577261738144448</v>
+        <v>1.123374567078389</v>
       </c>
       <c r="G94">
-        <v>-7.840342977505511</v>
+        <v>-7.203033166285954</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.721595880452453</v>
       </c>
       <c r="E95">
-        <v>-35.42039439334688</v>
+        <v>-36.37575296932307</v>
       </c>
       <c r="F95">
-        <v>0.06051043479219054</v>
+        <v>0.5978094130656171</v>
       </c>
       <c r="G95">
-        <v>-6.396802768925085</v>
+        <v>-8.004787706077728</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.09955399276805</v>
       </c>
       <c r="E96">
-        <v>-37.42944962261284</v>
+        <v>-39.39962337404893</v>
       </c>
       <c r="F96">
-        <v>0.1833838283842468</v>
+        <v>0.474868921713934</v>
       </c>
       <c r="G96">
-        <v>-7.256445508016555</v>
+        <v>-7.022254206022972</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.50067407088098</v>
       </c>
       <c r="E97">
-        <v>-40.01315235379312</v>
+        <v>-41.56491774929052</v>
       </c>
       <c r="F97">
-        <v>-0.3810756602921699</v>
+        <v>0.5312070171457313</v>
       </c>
       <c r="G97">
-        <v>-7.323689309010232</v>
+        <v>-7.531138024137582</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.91441648329585</v>
       </c>
       <c r="E98">
-        <v>-41.14075370288806</v>
+        <v>-42.91714725882493</v>
       </c>
       <c r="F98">
-        <v>0.07679365282902041</v>
+        <v>0.4335839187258095</v>
       </c>
       <c r="G98">
-        <v>-7.045394919342479</v>
+        <v>-8.182643454629535</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.32094473617396</v>
       </c>
       <c r="E99">
-        <v>-45.17582329657869</v>
+        <v>-45.35712981042379</v>
       </c>
       <c r="F99">
-        <v>-0.4847756619790288</v>
+        <v>0.4401520438626068</v>
       </c>
       <c r="G99">
-        <v>-6.925083073354285</v>
+        <v>-8.15750317180431</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.72338705022906</v>
       </c>
       <c r="E100">
-        <v>-45.36409460344758</v>
+        <v>-47.10469283659082</v>
       </c>
       <c r="F100">
-        <v>0.03579195149265329</v>
+        <v>0.3139287324936293</v>
       </c>
       <c r="G100">
-        <v>-7.96539883525148</v>
+        <v>-8.375797234118311</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.08029473681426</v>
       </c>
       <c r="E101">
-        <v>-47.78249444792588</v>
+        <v>-48.96910520969627</v>
       </c>
       <c r="F101">
-        <v>-0.306445555871754</v>
+        <v>0.151953912387228</v>
       </c>
       <c r="G101">
-        <v>-7.547607988195456</v>
+        <v>-8.501783355160816</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.41844108360062</v>
       </c>
       <c r="E102">
-        <v>-50.19882251554568</v>
+        <v>-50.59837204147944</v>
       </c>
       <c r="F102">
-        <v>-0.9217046755248505</v>
+        <v>-0.1575862768538773</v>
       </c>
       <c r="G102">
-        <v>-7.432040153965039</v>
+        <v>-8.559373605361978</v>
       </c>
     </row>
   </sheetData>
